--- a/survey_templates/048_product_review_questionnaire--survey_templates.xlsx
+++ b/survey_templates/048_product_review_questionnaire--survey_templates.xlsx
@@ -1,15 +1,15 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
-<workbook xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
+<workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <workbookPr/>
   <workbookProtection/>
   <bookViews>
     <workbookView visibility="visible" minimized="0" showHorizontalScroll="1" showVerticalScroll="1" showSheetTabs="1" tabRatio="600" firstSheet="0" activeTab="0" autoFilterDateGrouping="1"/>
   </bookViews>
   <sheets>
-    <sheet name="survey" sheetId="1" state="visible" r:id="rId1"/>
-    <sheet name="choices" sheetId="2" state="visible" r:id="rId2"/>
-    <sheet name="settings" sheetId="3" state="visible" r:id="rId3"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="survey" sheetId="1" state="visible" r:id="rId1"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="choices" sheetId="2" state="visible" r:id="rId2"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="settings" sheetId="3" state="visible" r:id="rId3"/>
   </sheets>
   <definedNames/>
   <calcPr calcId="124519" fullCalcOnLoad="1"/>
@@ -883,7 +883,7 @@
       </c>
       <c r="C2" t="inlineStr">
         <is>
-          <t>product_bought</t>
+          <t>product bought</t>
         </is>
       </c>
     </row>
@@ -900,7 +900,7 @@
       </c>
       <c r="C3" t="inlineStr">
         <is>
-          <t>service_bought</t>
+          <t>service bought</t>
         </is>
       </c>
     </row>
@@ -934,7 +934,7 @@
       </c>
       <c r="C5" t="inlineStr">
         <is>
-          <t>physical_store</t>
+          <t>physical store</t>
         </is>
       </c>
     </row>
@@ -951,7 +951,7 @@
       </c>
       <c r="C6" t="inlineStr">
         <is>
-          <t>online_store</t>
+          <t>online store</t>
         </is>
       </c>
     </row>
@@ -1036,7 +1036,7 @@
       </c>
       <c r="C11" t="inlineStr">
         <is>
-          <t>not_satisfied</t>
+          <t>not satisfied</t>
         </is>
       </c>
     </row>
@@ -1070,7 +1070,7 @@
       </c>
       <c r="C13" t="inlineStr">
         <is>
-          <t>not_recommended</t>
+          <t>not recommended</t>
         </is>
       </c>
     </row>
